--- a/artfynd/S 2895-2022 artfynd.xlsx
+++ b/artfynd/S 2895-2022 artfynd.xlsx
@@ -6978,7 +6978,7 @@
         <v>115554563</v>
       </c>
       <c r="B61" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>115554488</v>
       </c>
       <c r="B63" t="n">
-        <v>57945</v>
+        <v>58000</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>88109092</v>
       </c>
       <c r="B155" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>91990241</v>
       </c>
       <c r="B156" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>99768486</v>
       </c>
       <c r="B157" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>107832755</v>
       </c>
       <c r="B158" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>115869248</v>
       </c>
       <c r="B159" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>123373601</v>
       </c>
       <c r="B160" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>123373670</v>
       </c>
       <c r="B161" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>123540947</v>
       </c>
       <c r="B162" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>131066572</v>
       </c>
       <c r="B163" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>121514291</v>
       </c>
       <c r="B179" t="n">
-        <v>58592</v>
+        <v>58647</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>124297994</v>
       </c>
       <c r="B234" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>

--- a/artfynd/S 2895-2022 artfynd.xlsx
+++ b/artfynd/S 2895-2022 artfynd.xlsx
@@ -6978,7 +6978,7 @@
         <v>115554563</v>
       </c>
       <c r="B61" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>115554488</v>
       </c>
       <c r="B63" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>88109092</v>
       </c>
       <c r="B155" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>91990241</v>
       </c>
       <c r="B156" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>99768486</v>
       </c>
       <c r="B157" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>107832755</v>
       </c>
       <c r="B158" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>115869248</v>
       </c>
       <c r="B159" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>123373601</v>
       </c>
       <c r="B160" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>123373670</v>
       </c>
       <c r="B161" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>123540947</v>
       </c>
       <c r="B162" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>131066572</v>
       </c>
       <c r="B163" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>121514291</v>
       </c>
       <c r="B179" t="n">
-        <v>58647</v>
+        <v>58660</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>124297994</v>
       </c>
       <c r="B234" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>

--- a/artfynd/S 2895-2022 artfynd.xlsx
+++ b/artfynd/S 2895-2022 artfynd.xlsx
@@ -6978,7 +6978,7 @@
         <v>115554563</v>
       </c>
       <c r="B61" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>115554488</v>
       </c>
       <c r="B63" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>88109092</v>
       </c>
       <c r="B155" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>91990241</v>
       </c>
       <c r="B156" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>99768486</v>
       </c>
       <c r="B157" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>107832755</v>
       </c>
       <c r="B158" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>115869248</v>
       </c>
       <c r="B159" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>123373601</v>
       </c>
       <c r="B160" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>123373670</v>
       </c>
       <c r="B161" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>123540947</v>
       </c>
       <c r="B162" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>131066572</v>
       </c>
       <c r="B163" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>121514291</v>
       </c>
       <c r="B179" t="n">
-        <v>58660</v>
+        <v>58662</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>124297994</v>
       </c>
       <c r="B234" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>

--- a/artfynd/S 2895-2022 artfynd.xlsx
+++ b/artfynd/S 2895-2022 artfynd.xlsx
@@ -7006,11 +7006,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7256,11 +7252,7 @@
       <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -17224,16 +17216,8 @@
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Timrå, Mpd</t>
@@ -17352,11 +17336,7 @@
       </c>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -17465,16 +17445,8 @@
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -17594,11 +17566,7 @@
       </c>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -17722,11 +17690,7 @@
       </c>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -17845,16 +17809,8 @@
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
@@ -17973,16 +17929,8 @@
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
@@ -18102,11 +18050,7 @@
       </c>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -18230,11 +18174,7 @@
       </c>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
@@ -20083,11 +20023,7 @@
       </c>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
@@ -26235,11 +26171,7 @@
       </c>
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M234" t="inlineStr"/>
       <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>

--- a/artfynd/S 2895-2022 artfynd.xlsx
+++ b/artfynd/S 2895-2022 artfynd.xlsx
@@ -6978,7 +6978,7 @@
         <v>115554563</v>
       </c>
       <c r="B61" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>115554488</v>
       </c>
       <c r="B63" t="n">
-        <v>58015</v>
+        <v>58025</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>88109092</v>
       </c>
       <c r="B155" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>91990241</v>
       </c>
       <c r="B156" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>99768486</v>
       </c>
       <c r="B157" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>107832755</v>
       </c>
       <c r="B158" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>115869248</v>
       </c>
       <c r="B159" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>123373601</v>
       </c>
       <c r="B160" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>123373670</v>
       </c>
       <c r="B161" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>123540947</v>
       </c>
       <c r="B162" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>131066572</v>
       </c>
       <c r="B163" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>121514291</v>
       </c>
       <c r="B179" t="n">
-        <v>58662</v>
+        <v>58672</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>124297994</v>
       </c>
       <c r="B234" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>

--- a/artfynd/S 2895-2022 artfynd.xlsx
+++ b/artfynd/S 2895-2022 artfynd.xlsx
@@ -6978,7 +6978,7 @@
         <v>115554563</v>
       </c>
       <c r="B61" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>115554488</v>
       </c>
       <c r="B63" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>88109092</v>
       </c>
       <c r="B155" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>91990241</v>
       </c>
       <c r="B156" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>99768486</v>
       </c>
       <c r="B157" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>107832755</v>
       </c>
       <c r="B158" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>115869248</v>
       </c>
       <c r="B159" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>123373601</v>
       </c>
       <c r="B160" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>123373670</v>
       </c>
       <c r="B161" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>123540947</v>
       </c>
       <c r="B162" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>131066572</v>
       </c>
       <c r="B163" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>121514291</v>
       </c>
       <c r="B179" t="n">
-        <v>58672</v>
+        <v>58674</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>124297994</v>
       </c>
       <c r="B234" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>

--- a/artfynd/S 2895-2022 artfynd.xlsx
+++ b/artfynd/S 2895-2022 artfynd.xlsx
@@ -6978,7 +6978,7 @@
         <v>115554563</v>
       </c>
       <c r="B61" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>115554488</v>
       </c>
       <c r="B63" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>88109092</v>
       </c>
       <c r="B155" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>91990241</v>
       </c>
       <c r="B156" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>99768486</v>
       </c>
       <c r="B157" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>107832755</v>
       </c>
       <c r="B158" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>115869248</v>
       </c>
       <c r="B159" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>123373601</v>
       </c>
       <c r="B160" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>123373670</v>
       </c>
       <c r="B161" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>123540947</v>
       </c>
       <c r="B162" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>131066572</v>
       </c>
       <c r="B163" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>121514291</v>
       </c>
       <c r="B179" t="n">
-        <v>58674</v>
+        <v>58676</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>124297994</v>
       </c>
       <c r="B234" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>

--- a/artfynd/S 2895-2022 artfynd.xlsx
+++ b/artfynd/S 2895-2022 artfynd.xlsx
@@ -17763,7 +17763,7 @@
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Mattias Edman, Mikael Gudrunsson</t>
+          <t>Mikael Gudrunsson, Mattias Edman</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>

--- a/artfynd/S 2895-2022 artfynd.xlsx
+++ b/artfynd/S 2895-2022 artfynd.xlsx
@@ -17763,7 +17763,7 @@
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson, Mattias Edman</t>
+          <t>Mattias Edman, Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>

--- a/artfynd/S 2895-2022 artfynd.xlsx
+++ b/artfynd/S 2895-2022 artfynd.xlsx
@@ -6978,7 +6978,7 @@
         <v>115554563</v>
       </c>
       <c r="B61" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>115554488</v>
       </c>
       <c r="B63" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>88109092</v>
       </c>
       <c r="B155" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>91990241</v>
       </c>
       <c r="B156" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>99768486</v>
       </c>
       <c r="B157" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>107832755</v>
       </c>
       <c r="B158" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>115869248</v>
       </c>
       <c r="B159" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>123373601</v>
       </c>
       <c r="B160" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>123373670</v>
       </c>
       <c r="B161" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>123540947</v>
       </c>
       <c r="B162" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>131066572</v>
       </c>
       <c r="B163" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>121514291</v>
       </c>
       <c r="B179" t="n">
-        <v>58676</v>
+        <v>58679</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>124297994</v>
       </c>
       <c r="B234" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
